--- a/編成番号.xlsx
+++ b/編成番号.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdc2a3472a7fa3ef/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdc2a3472a7fa3ef/Java/github用/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="101" documentId="8_{BD7F7EC6-977D-42C7-AA54-F44581F0AE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D5F4B76-53C1-4B1C-808B-50010A46CBF3}"/>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="35.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
